--- a/sheets/조재수대금교본/검수/무명배우.xlsx
+++ b/sheets/조재수대금교본/검수/무명배우.xlsx
@@ -4832,8 +4832,7 @@
       <c r="O4" s="23"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⊏
-太</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="Q4" s="23"/>
@@ -4846,8 +4845,7 @@
       <c r="S4" s="23"/>
       <c r="T4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⊏
-太</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="U4" s="23"/>
@@ -5085,8 +5083,7 @@
       <c r="O8" s="23"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⊏
-太</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="Q8" s="23"/>
@@ -5099,8 +5096,7 @@
       <c r="S8" s="23"/>
       <c r="T8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⊏
-太</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="U8" s="23"/>
@@ -5146,8 +5142,7 @@
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="C10" s="24"/>
@@ -5272,11 +5267,7 @@
         </is>
       </c>
       <c r="G12" s="23"/>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H12" s="21"/>
       <c r="I12" s="23"/>
       <c r="J12" s="21"/>
       <c r="K12" s="23"/>
@@ -5296,8 +5287,7 @@
       <c r="O12" s="23"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⊏
-太</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="Q12" s="23"/>
@@ -5310,8 +5300,7 @@
       <c r="S12" s="23"/>
       <c r="T12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⊏
-太</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="U12" s="23"/>
@@ -5323,7 +5312,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲ㄴ</t>
+仲</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -5351,7 +5340,7 @@
       <c r="M13" s="23"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲ㄴ</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="O13" s="23"/>
@@ -5364,7 +5353,7 @@
       <c r="Q13" s="23"/>
       <c r="R13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲ㄴ
+          <t xml:space="preserve">仲
 林</t>
         </is>
       </c>
@@ -5600,8 +5589,8 @@
       <c r="E18" s="24"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲ㄴ
-仲ㄴ</t>
+          <t xml:space="preserve">仲
+仲</t>
         </is>
       </c>
       <c r="G18" s="24"/>
@@ -5644,11 +5633,7 @@
         </is>
       </c>
       <c r="S18" s="24"/>
-      <c r="T18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T18" s="21"/>
       <c r="U18" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/무명배우.xlsx
+++ b/sheets/조재수대금교본/검수/무명배우.xlsx
@@ -4832,7 +4832,8 @@
       <c r="O4" s="23"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">⊏
+太</t>
         </is>
       </c>
       <c r="Q4" s="23"/>
@@ -4845,7 +4846,8 @@
       <c r="S4" s="23"/>
       <c r="T4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">⊏
+太</t>
         </is>
       </c>
       <c r="U4" s="23"/>
@@ -5083,7 +5085,8 @@
       <c r="O8" s="23"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">⊏
+太</t>
         </is>
       </c>
       <c r="Q8" s="23"/>
@@ -5096,7 +5099,8 @@
       <c r="S8" s="23"/>
       <c r="T8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">⊏
+太</t>
         </is>
       </c>
       <c r="U8" s="23"/>
@@ -5287,7 +5291,8 @@
       <c r="O12" s="23"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">⊏
+太</t>
         </is>
       </c>
       <c r="Q12" s="23"/>
@@ -5300,7 +5305,8 @@
       <c r="S12" s="23"/>
       <c r="T12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">⊏
+太</t>
         </is>
       </c>
       <c r="U12" s="23"/>
@@ -5312,7 +5318,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲</t>
+仲ㄴ</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -5340,7 +5346,7 @@
       <c r="M13" s="23"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲ㄴ</t>
         </is>
       </c>
       <c r="O13" s="23"/>
@@ -5353,7 +5359,7 @@
       <c r="Q13" s="23"/>
       <c r="R13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
+          <t xml:space="preserve">仲ㄴ
 林</t>
         </is>
       </c>
@@ -5589,8 +5595,8 @@
       <c r="E18" s="24"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-仲</t>
+          <t xml:space="preserve">仲ㄴ
+仲ㄴ</t>
         </is>
       </c>
       <c r="G18" s="24"/>

--- a/sheets/조재수대금교본/검수/무명배우.xlsx
+++ b/sheets/조재수대금교본/검수/무명배우.xlsx
@@ -4697,32 +4697,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="89.42" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21"/>
       <c r="C3" s="22"/>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="89.42" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="89.42" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="89.42" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
       <c r="T6" s="21"/>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="89.42" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="89.42" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="89.42" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="U9" s="23"/>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="89.42" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="24"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="89.42" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="89.42" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="U12" s="23"/>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="89.42" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="89.42" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="U14" s="24"/>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="89.42" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="89.42" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="23"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="89.42" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -5577,7 +5577,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="23"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="89.42" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -5648,6 +5648,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
 </worksheet>
 </file>